--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5356,6 +5356,125 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123412399</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86053</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1615</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk stjälkröksvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tulostoma melanocyclum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bres.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gårdby sandhed, Öl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>601049</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6276539</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gårdby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>betad sandstäpp</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>123412399</v>
       </c>
       <c r="B39" t="n">
-        <v>86053</v>
+        <v>86055</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>123412399</v>
       </c>
       <c r="B39" t="n">
-        <v>86055</v>
+        <v>86057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>123412399</v>
       </c>
       <c r="B39" t="n">
-        <v>86060</v>
+        <v>86074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>123412399</v>
       </c>
       <c r="B39" t="n">
-        <v>86074</v>
+        <v>86079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>123412399</v>
       </c>
       <c r="B39" t="n">
-        <v>86079</v>
+        <v>86081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5475,6 +5475,108 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125168508</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99758</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sandtimotej</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phleum arenarium</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gårdby sandheds naturreservat, Öl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>601069</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6276520</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gårdby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>125168508</v>
       </c>
       <c r="B40" t="n">
-        <v>99758</v>
+        <v>99928</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5480,12 +5480,7 @@
         <v>125168508</v>
       </c>
       <c r="B40" t="n">
-        <v>99928</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5576,6 +5571,103 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125873636</v>
+      </c>
+      <c r="B41" t="n">
+        <v>108873</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>601097</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6276506</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gårdby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>125168508</v>
       </c>
       <c r="B40" t="n">
-        <v>99983</v>
+        <v>99990</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108873</v>
+        <v>108880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108880</v>
+        <v>108881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108881</v>
+        <v>108883</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108883</v>
+        <v>108887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108887</v>
+        <v>108888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108888</v>
+        <v>108890</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Ove Grönlund, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108890</v>
+        <v>108892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ove Grönlund, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Ove Grönlund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108892</v>
+        <v>108896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108896</v>
+        <v>108909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108909</v>
+        <v>108912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -5577,7 +5577,7 @@
         <v>125873636</v>
       </c>
       <c r="B41" t="n">
-        <v>108912</v>
+        <v>108921</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -3499,7 +3499,7 @@
         <v>125940660</v>
       </c>
       <c r="B27" t="n">
-        <v>30568</v>
+        <v>30573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/233270</t>
         </is>
       </c>
     </row>
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/240626</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/446345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/446346</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/308352</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412399</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946770</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132868082</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/635973</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54136158</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2118,6 +2183,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946789</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125168508</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98135249</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2425,6 +2505,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>BSIS-exkursion</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134635235</t>
         </is>
       </c>
     </row>
@@ -2548,6 +2633,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78876850</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2662,6 +2752,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67263366</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2783,6 +2878,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78876254</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2898,6 +2998,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877763</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14216453</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3127,6 +3237,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70551999</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3242,6 +3357,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877437</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3368,6 +3488,11 @@
           <t>Personlig inventering NES</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91366160</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3493,6 +3618,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132686520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3618,6 +3748,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125940660</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3737,6 +3872,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94824102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3867,6 +4007,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132686496</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3997,6 +4142,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116368544</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4112,6 +4262,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117088512</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4221,6 +4376,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81631800</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4350,6 +4510,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089937</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4457,6 +4622,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101765495</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4596,6 +4766,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97292096</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4707,6 +4882,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101765511</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4832,6 +5012,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111101304</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4949,6 +5134,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78876826</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5060,6 +5250,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15750705</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5188,6 +5383,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17066601</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5312,6 +5512,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430543</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5415,6 +5620,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90973717</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5539,6 +5749,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70552057</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5660,6 +5875,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78876600</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5767,6 +5987,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101765510</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5887,6 +6112,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111198338</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5998,6 +6228,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15750722</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6101,6 +6336,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91021113</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6225,6 +6465,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70552066</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6332,6 +6577,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101765489</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6439,6 +6689,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101765499</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6548,6 +6803,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2923897</t>
         </is>
       </c>
     </row>
@@ -6659,6 +6919,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60558553</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6769,6 +7034,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72341660</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6884,6 +7154,11 @@
           <t>Botanikdagarna 2022 på Öland</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102606674</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6997,6 +7272,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16768534</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7110,6 +7390,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53995374</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7222,6 +7507,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124923374</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7333,6 +7623,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946986</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7430,6 +7725,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873636</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7536,6 +7836,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72341663</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7642,6 +7947,11 @@
           <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90968272</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7752,6 +8062,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87452574</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7864,6 +8179,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60558453</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7975,6 +8295,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5141664</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8081,6 +8406,11 @@
       <c r="AY66" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54136165</t>
         </is>
       </c>
     </row>
@@ -8190,6 +8520,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946779</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8301,6 +8636,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125545586</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8413,6 +8753,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6181704</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8534,8 +8879,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62497754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -3629,7 +3629,7 @@
         <v>125940660</v>
       </c>
       <c r="B27" t="n">
-        <v>30573</v>
+        <v>30576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ70"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>635973</v>
+        <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>100693</v>
+        <v>87096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,37 +1852,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1888</v>
+        <v>1615</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Mörk stjälkröksvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Tulostoma melanocyclum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Bres.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gårdby sandhed (16), Öl</t>
+          <t>Gårdby sandhed , Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601043</v>
+        <v>601055</v>
       </c>
       <c r="R12" t="n">
-        <v>6276537</v>
+        <v>6276536</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,19 +1915,19 @@
           <t>Gårdby</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Hö-Mör-0159</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,39 +1936,36 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>sandstäpp</t>
+          <t>betad sandgräshed</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Öland- Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/635973</t>
+          <t>https://artportalen.se/Sighting/136475997</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54136158</v>
+        <v>635973</v>
       </c>
       <c r="B13" t="n">
         <v>100693</v>
@@ -1986,23 +1994,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO., Öl</t>
+          <t>Gårdby sandhed (16), Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601088</v>
+        <v>601043</v>
       </c>
       <c r="R13" t="n">
-        <v>6276505</v>
+        <v>6276537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,14 +2028,19 @@
           <t>Gårdby</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Hö-Mör-0159</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,85 +2052,84 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Sandstäpp</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Via Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54136158</t>
+          <t>https://artportalen.se/Sighting/635973</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124946789</v>
+        <v>54136158</v>
       </c>
       <c r="B14" t="n">
-        <v>100795</v>
+        <v>100693</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1900</v>
+        <v>1888</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandtimotej</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phleum arenarium</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR, Öl</t>
+          <t>Gårdby sandhed NO., Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601035</v>
+        <v>601088</v>
       </c>
       <c r="R14" t="n">
-        <v>6276550</v>
+        <v>6276505</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,12 +2153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,36 +2167,39 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>betad sandgräshed</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Sandstäpp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heléne Wertwein Haavikko, Stefan Svenaeus, Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946789</t>
+          <t>https://artportalen.se/Sighting/54136158</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125168508</v>
+        <v>124946789</v>
       </c>
       <c r="B15" t="n">
         <v>100795</v>
@@ -2220,19 +2228,27 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gårdby sandheds naturreservat, Öl</t>
+          <t>Gårdby sandhed NR, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601069</v>
+        <v>601035</v>
       </c>
       <c r="R15" t="n">
-        <v>6276520</v>
+        <v>6276550</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,12 +2272,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,74 +2286,77 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>betad sandgräshed</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Janne Kolehmainen, Pontus Axén</t>
+          <t>Heléne Wertwein Haavikko, Stefan Svenaeus, Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125168508</t>
+          <t>https://artportalen.se/Sighting/124946789</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98135249</v>
+        <v>125168508</v>
       </c>
       <c r="B16" t="n">
-        <v>89085</v>
+        <v>100795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4379</v>
+        <v>1900</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Sandtimotej</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Phleum arenarium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
+          <t>Gårdby sandheds naturreservat, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601111</v>
+        <v>601069</v>
       </c>
       <c r="R16" t="n">
-        <v>6276524</v>
+        <v>6276520</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2356,17 +2375,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1993-09-21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1993-09-21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,39 +2394,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>På kalkrik sand med sparsam Koeleria-veg. på gamla järnvägsvallen genom tallskogen.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Janne Kolehmainen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Knutsson, Karl-göran Bringer</t>
+          <t>Janne Kolehmainen, Pontus Axén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98135249</t>
+          <t>https://artportalen.se/Sighting/125168508</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134635235</v>
+        <v>98135249</v>
       </c>
       <c r="B17" t="n">
-        <v>57921</v>
+        <v>89085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,37 +2428,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100067</v>
+        <v>4379</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601058</v>
+        <v>601111</v>
       </c>
       <c r="R17" t="n">
-        <v>6276542</v>
+        <v>6276524</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,12 +2485,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>1993-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>1993-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,93 +2499,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>sandstäpp</t>
+          <t>På kalkrik sand med sparsam Koeleria-veg. på gamla järnvägsvallen genom tallskogen.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Anders Källberg, Ann-Sofie Åsander, Christina Stenberg, Eva Grönlund, Gunnar Noren, Gunnel Ström, Karin Hendahl, Leif lagerstedt, Margareta Danielsson, Patrik Engström, Per Johnsson, Rolf Wahlström, Susanne Rosengren, Lisa Lundin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>BSIS-exkursion</t>
-        </is>
-      </c>
+          <t>Tommy Knutsson, Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134635235</t>
+          <t>https://artportalen.se/Sighting/98135249</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>78876850</v>
+        <v>134635235</v>
       </c>
       <c r="B18" t="n">
-        <v>43908</v>
+        <v>57921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100370</v>
+        <v>100067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skiktdynemott</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apomyelois bistriatella</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hulst, 1887)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601040</v>
+        <v>601058</v>
       </c>
       <c r="R18" t="n">
-        <v>6276621</v>
+        <v>6276542</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,22 +2593,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>02:30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,34 +2607,42 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Anders Källberg, Ann-Sofie Åsander, Christina Stenberg, Eva Grönlund, Gunnar Noren, Gunnel Ström, Karin Hendahl, Leif lagerstedt, Margareta Danielsson, Patrik Engström, Per Johnsson, Rolf Wahlström, Susanne Rosengren, Lisa Lundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>BSIS-exkursion</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876850</t>
+          <t>https://artportalen.se/Sighting/134635235</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67263366</v>
+        <v>78876850</v>
       </c>
       <c r="B19" t="n">
-        <v>44113</v>
+        <v>43908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2652,21 +2650,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100437</v>
+        <v>100370</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klocksäckspinnare</t>
+          <t>Skiktdynemott</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bacotia claustrella</t>
+          <t>Apomyelois bistriatella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bruand, 1845)</t>
+          <t>(Hulst, 1887)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2675,31 +2673,27 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>bankning</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601087</v>
+        <v>601040</v>
       </c>
       <c r="R19" t="n">
-        <v>6276560</v>
+        <v>6276621</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,12 +2717,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,55 +2741,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67263366</t>
+          <t>https://artportalen.se/Sighting/78876850</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>78876254</v>
+        <v>67263366</v>
       </c>
       <c r="B20" t="n">
-        <v>41689</v>
+        <v>44113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100562</v>
+        <v>100437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbandad fältmätare</t>
+          <t>Klocksäckspinnare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Catarhoe rubidata</t>
+          <t>Bacotia claustrella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Bruand, 1845)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,27 +2799,31 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>bankning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>N Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601040</v>
+        <v>601087</v>
       </c>
       <c r="R20" t="n">
-        <v>6276621</v>
+        <v>6276560</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2838,22 +2847,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>02:30</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,34 +2861,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876254</t>
+          <t>https://artportalen.se/Sighting/67263366</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877763</v>
+        <v>78876254</v>
       </c>
       <c r="B21" t="n">
-        <v>8203</v>
+        <v>41689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,21 +2895,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100704</v>
+        <v>100562</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sandspolvivel</t>
+          <t>Rödbandad fältmätare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Coniocleonus turbatus</t>
+          <t>Catarhoe rubidata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fåhraeus, 1842)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2920,31 +2918,27 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601059</v>
+        <v>601040</v>
       </c>
       <c r="R21" t="n">
-        <v>6276518</v>
+        <v>6276621</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2963,17 +2957,27 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,49 +2993,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125877763</t>
+          <t>https://artportalen.se/Sighting/78876254</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14216453</v>
+        <v>125877763</v>
       </c>
       <c r="B22" t="n">
-        <v>9660</v>
+        <v>8203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100708</v>
+        <v>100704</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Månhornsbagge</t>
+          <t>Sandspolvivel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copris lunaris</t>
+          <t>Coniocleonus turbatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fåhraeus, 1842)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3039,19 +3043,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gï¿½rdby Sand, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600994</v>
+        <v>601059</v>
       </c>
       <c r="R22" t="n">
-        <v>6276562</v>
+        <v>6276518</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3075,17 +3092,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-06-02</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-06-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Pï¿½ uppdrag av Lï¿½nsstyrelsen i Kalmar Lï¿½n</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,94 +3106,73 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>nï¿½tspillning sandig ljunghed</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Naturcentrum AB</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14216453</t>
+          <t>https://artportalen.se/Sighting/125877763</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>70551999</v>
+        <v>14216453</v>
       </c>
       <c r="B23" t="n">
-        <v>41416</v>
+        <v>9660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101061</v>
+        <v>100708</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smaragdgrön lundmätare</t>
+          <t>Månhornsbagge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hemistola chrysoprasaria</t>
+          <t>Copris lunaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Esper, 1795)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>lampa</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gï¿½rdby Sand, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600995</v>
+        <v>600994</v>
       </c>
       <c r="R23" t="n">
-        <v>6276588</v>
+        <v>6276562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3203,17 +3194,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
+          <t>2009-06-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
+          <t>2009-06-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Pï¿½ uppdrag av Lï¿½nsstyrelsen i Kalmar Lï¿½n</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,58 +3220,67 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>nï¿½tspillning sandig ljunghed</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Naturcentrum AB</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Annette Bludau, Fred Ockruck</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70551999</t>
+          <t>https://artportalen.se/Sighting/14216453</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877437</v>
+        <v>70551999</v>
       </c>
       <c r="B24" t="n">
-        <v>8244</v>
+        <v>41416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101201</v>
+        <v>101061</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blyvivel</t>
+          <t>Smaragdgrön lundmätare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepyrus capucinus</t>
+          <t>Hemistola chrysoprasaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Esper, 1795)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3285,25 +3290,25 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601059</v>
+        <v>600995</v>
       </c>
       <c r="R24" t="n">
-        <v>6276518</v>
+        <v>6276588</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3322,17 +3327,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,34 +3346,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Annette Bludau, Fred Ockruck</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125877437</t>
+          <t>https://artportalen.se/Sighting/70551999</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91366160</v>
+        <v>125877437</v>
       </c>
       <c r="B25" t="n">
-        <v>13045</v>
+        <v>8244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,21 +3380,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101225</v>
+        <v>101201</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Öländsk svävfluga</t>
+          <t>Blyvivel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lomatia lateralis</t>
+          <t>Lepyrus capucinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Meigen, 1820)</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3398,29 +3402,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gårdby Sandstäpp, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601081</v>
+        <v>601059</v>
       </c>
       <c r="R25" t="n">
-        <v>6276523</v>
+        <v>6276518</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3439,17 +3446,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,48 +3465,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>sandstäpp</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>Erik Sjödin</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Personlig inventering NES</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91366160</t>
+          <t>https://artportalen.se/Sighting/125877437</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132686520</v>
+        <v>91366160</v>
       </c>
       <c r="B26" t="n">
-        <v>41740</v>
+        <v>13045</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,21 +3500,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101256</v>
+        <v>101225</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre purpurmätare</t>
+          <t>Öländsk svävfluga</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lythria cruentaria</t>
+          <t>Lomatia lateralis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Meigen, 1820)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3529,29 +3522,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601031</v>
+        <v>601081</v>
       </c>
       <c r="R26" t="n">
-        <v>6276536</v>
+        <v>6276523</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3573,27 +3563,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2020-07-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2020-07-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3602,56 +3582,70 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>sandstäpp</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Personlig inventering NES</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132686520</t>
+          <t>https://artportalen.se/Sighting/91366160</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125940660</v>
+        <v>132686520</v>
       </c>
       <c r="B27" t="n">
-        <v>30576</v>
+        <v>41740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101668</v>
+        <v>101256</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandgeting</t>
+          <t>Mindre purpurmätare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pterocheilus phaleratus</t>
+          <t>Lythria cruentaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Panzer, 1797)</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3674,17 +3668,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601044</v>
+        <v>601031</v>
       </c>
       <c r="R27" t="n">
-        <v>6276529</v>
+        <v>6276536</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3708,22 +3702,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,49 +3733,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Edvin Klein, Ove Grönlund, Simon Stenberg Jönsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125940660</t>
+          <t>https://artportalen.se/Sighting/132686520</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>94824102</v>
+        <v>125940660</v>
       </c>
       <c r="B28" t="n">
-        <v>42206</v>
+        <v>30576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101814</v>
+        <v>101668</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Streckhedspinnare</t>
+          <t>Sandgeting</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spiris striata</t>
+          <t>Pterocheilus phaleratus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Panzer, 1797)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3795,30 +3789,26 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601031</v>
+        <v>601044</v>
       </c>
       <c r="R28" t="n">
-        <v>6276536</v>
+        <v>6276529</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3842,12 +3832,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,44 +3863,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Jon Liljebäck, Edvin Klein, Ove Grönlund, Simon Stenberg Jönsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94824102</t>
+          <t>https://artportalen.se/Sighting/125940660</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132686496</v>
+        <v>94824102</v>
       </c>
       <c r="B29" t="n">
-        <v>29446</v>
+        <v>42206</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102702</v>
+        <v>101814</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mosshumla</t>
+          <t>Streckhedspinnare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bombus muscorum</t>
+          <t>Spiris striata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3919,10 +3919,14 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3962,27 +3966,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På fältsippa</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4003,22 +3992,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132686496</t>
+          <t>https://artportalen.se/Sighting/94824102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116368544</v>
+        <v>132686496</v>
       </c>
       <c r="B30" t="n">
-        <v>43435</v>
+        <v>29446</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4026,16 +4015,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102922</v>
+        <v>102702</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ängsnätfjäril</t>
+          <t>Mosshumla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Melitaea cinxia</t>
+          <t>Bombus muscorum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4045,35 +4034,35 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gårdby sandheds naturreservat, Gårdby sandheds naturreservat, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601036</v>
+        <v>601031</v>
       </c>
       <c r="R30" t="n">
-        <v>6276538</v>
+        <v>6276536</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4097,27 +4086,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Larverna spridda på någon m2.</t>
+          <t>På fältsippa</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4133,24 +4122,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116368544</t>
+          <t>https://artportalen.se/Sighting/132686496</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117088512</v>
+        <v>116368544</v>
       </c>
       <c r="B31" t="n">
         <v>43435</v>
@@ -4180,35 +4169,35 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandheds naturreservat, Gårdby sandheds naturreservat, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601031</v>
+        <v>601036</v>
       </c>
       <c r="R31" t="n">
-        <v>6276536</v>
+        <v>6276538</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4232,12 +4221,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Larverna spridda på någon m2.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4253,27 +4257,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117088512</t>
+          <t>https://artportalen.se/Sighting/116368544</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>81631800</v>
+        <v>117088512</v>
       </c>
       <c r="B32" t="n">
-        <v>58586</v>
+        <v>43435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4281,49 +4285,54 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103051</v>
+        <v>102922</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Ängsnätfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Melitaea cinxia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601111</v>
+        <v>601031</v>
       </c>
       <c r="R32" t="n">
-        <v>6276524</v>
+        <v>6276536</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4342,17 +4351,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1987-05-28</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1987-05-28</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4361,33 +4370,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tommy Knutsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81631800</t>
+          <t>https://artportalen.se/Sighting/117088512</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102089937</v>
+        <v>81631800</v>
       </c>
       <c r="B33" t="n">
-        <v>43310</v>
+        <v>58586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,21 +4405,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>201145</v>
+        <v>103051</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Väpplingblåvinge</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polyommatus dorylas</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4417,36 +4427,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Strax NO om Gårdby sandhed, bara några meter från sn.gr., Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601031</v>
+        <v>601111</v>
       </c>
       <c r="R33" t="n">
-        <v>6276536</v>
+        <v>6276524</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4465,27 +4466,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>1987-05-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>1987-05-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4494,34 +4485,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089937</t>
+          <t>https://artportalen.se/Sighting/81631800</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101765495</v>
+        <v>102089937</v>
       </c>
       <c r="B34" t="n">
-        <v>41060</v>
+        <v>43310</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,16 +4519,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>214757</v>
+        <v>201145</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bågstreckad näbbmal</t>
+          <t>Väpplingblåvinge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sophronia humerella</t>
+          <t>Polyommatus dorylas</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4546,29 +4536,41 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601080</v>
+        <v>601031</v>
       </c>
       <c r="R34" t="n">
-        <v>6276524</v>
+        <v>6276536</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4587,17 +4589,27 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4613,86 +4625,74 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765495</t>
+          <t>https://artportalen.se/Sighting/102089937</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97292096</v>
+        <v>101765495</v>
       </c>
       <c r="B35" t="n">
-        <v>44833</v>
+        <v>41060</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>214907</v>
+        <v>214757</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Större vitbandsvecklare</t>
+          <t>Bågstreckad näbbmal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Xerocnephasia rigana</t>
+          <t>Sophronia humerella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sodoffsky, 1829)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR N, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601106</v>
+        <v>601080</v>
       </c>
       <c r="R35" t="n">
-        <v>6276509</v>
+        <v>6276524</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4716,27 +4716,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>20:32</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>vid parkeringen</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4749,60 +4734,59 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Sandgräsmark</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97292096</t>
+          <t>https://artportalen.se/Sighting/101765495</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101765511</v>
+        <v>97292096</v>
       </c>
       <c r="B36" t="n">
-        <v>44549</v>
+        <v>44833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>215095</v>
+        <v>214907</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Månskärerotvecklare</t>
+          <t>Större vitbandsvecklare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelochrista huebneriana</t>
+          <t>Xerocnephasia rigana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lienig &amp; Zeller, 1846)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Sodoffsky, 1829)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -4810,25 +4794,29 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed NR N, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601080</v>
+        <v>601106</v>
       </c>
       <c r="R36" t="n">
-        <v>6276524</v>
+        <v>6276509</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4852,12 +4840,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>vid parkeringen</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4870,27 +4873,32 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Sandgräsmark</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Kaj Svahn</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765511</t>
+          <t>https://artportalen.se/Sighting/97292096</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111101304</v>
+        <v>101765511</v>
       </c>
       <c r="B37" t="n">
         <v>44549</v>
@@ -4918,11 +4926,7 @@
           <t>(Lienig &amp; Zeller, 1846)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -4930,22 +4934,22 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, skogsvägen norr om, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601026</v>
+        <v>601080</v>
       </c>
       <c r="R37" t="n">
-        <v>6276537</v>
+        <v>6276524</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4967,27 +4971,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5003,27 +4997,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
+          <t>Jesper Hansson, Kaj Svahn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111101304</t>
+          <t>https://artportalen.se/Sighting/101765511</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>78876826</v>
+        <v>111101304</v>
       </c>
       <c r="B38" t="n">
-        <v>43981</v>
+        <v>44549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5031,46 +5025,54 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>215320</v>
+        <v>215095</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brokigt timjansmott</t>
+          <t>Månskärerotvecklare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pempeliella ornatella</t>
+          <t>Pelochrista huebneriana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Lienig &amp; Zeller, 1846)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandhed, skogsvägen norr om, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601040</v>
+        <v>601026</v>
       </c>
       <c r="R38" t="n">
-        <v>6276621</v>
+        <v>6276537</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5089,27 +5091,27 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5125,27 +5127,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876826</t>
+          <t>https://artportalen.se/Sighting/111101304</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15750705</v>
+        <v>78876826</v>
       </c>
       <c r="B39" t="n">
-        <v>41758</v>
+        <v>43981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,33 +5155,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>215656</v>
+        <v>215320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Brokigt timjansmott</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Pempeliella ornatella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5187,17 +5184,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>600995</v>
+        <v>601040</v>
       </c>
       <c r="R39" t="n">
-        <v>6276588</v>
+        <v>6276621</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5221,12 +5218,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2013-07-29</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2013-07-30</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5235,30 +5242,31 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15750705</t>
+          <t>https://artportalen.se/Sighting/78876826</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17066601</v>
+        <v>15750705</v>
       </c>
       <c r="B40" t="n">
         <v>41758</v>
@@ -5288,21 +5296,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5310,17 +5311,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601075</v>
+        <v>600995</v>
       </c>
       <c r="R40" t="n">
-        <v>6276530</v>
+        <v>6276588</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5344,22 +5345,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2013-07-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5374,27 +5365,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Per Gustafsson, Tobias Hammarberg, David Hammarberg, Johan Södercrantz</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17066601</t>
+          <t>https://artportalen.se/Sighting/15750705</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>70430543</v>
+        <v>17066601</v>
       </c>
       <c r="B41" t="n">
-        <v>41451</v>
+        <v>41758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5402,16 +5393,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215683</v>
+        <v>215656</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5431,7 +5422,11 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -5439,17 +5434,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>600995</v>
+        <v>601075</v>
       </c>
       <c r="R41" t="n">
-        <v>6276588</v>
+        <v>6276530</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5473,22 +5468,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-06-28</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5503,27 +5498,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Per Gustafsson, Tobias Hammarberg, David Hammarberg, Johan Södercrantz</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70430543</t>
+          <t>https://artportalen.se/Sighting/17066601</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>90973717</v>
+        <v>70430543</v>
       </c>
       <c r="B42" t="n">
-        <v>41695</v>
+        <v>41451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5531,39 +5526,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>215701</v>
+        <v>215683</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre mårfältmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epirrhoe hastulata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hübner, 1790)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601042</v>
+        <v>600995</v>
       </c>
       <c r="R42" t="n">
-        <v>6276516</v>
+        <v>6276588</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5585,17 +5592,27 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2014-06-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5604,34 +5621,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90973717</t>
+          <t>https://artportalen.se/Sighting/70430543</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>70552057</v>
+        <v>90973717</v>
       </c>
       <c r="B43" t="n">
-        <v>41623</v>
+        <v>41695</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5639,51 +5655,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>215755</v>
+        <v>215701</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Längsbandad strimmätare</t>
+          <t>Mindre mårfältmätare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Horisme vitalbata</t>
+          <t>Epirrhoe hastulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hübner, 1790)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>600995</v>
+        <v>601042</v>
       </c>
       <c r="R43" t="n">
-        <v>6276588</v>
+        <v>6276516</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5705,27 +5709,17 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5734,30 +5728,31 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70552057</t>
+          <t>https://artportalen.se/Sighting/90973717</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>78876600</v>
+        <v>70552057</v>
       </c>
       <c r="B44" t="n">
         <v>41623</v>
@@ -5787,11 +5782,15 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
@@ -5801,17 +5800,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601040</v>
+        <v>600995</v>
       </c>
       <c r="R44" t="n">
-        <v>6276621</v>
+        <v>6276588</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5835,22 +5834,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2014-07-02</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5859,31 +5858,30 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Krister Aronsson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Krister Aronsson, Håkan Lernefalk</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78876600</t>
+          <t>https://artportalen.se/Sighting/70552057</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>101765510</v>
+        <v>78876600</v>
       </c>
       <c r="B45" t="n">
         <v>41623</v>
@@ -5911,29 +5909,33 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby Sandhed, Tallskog N om, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601080</v>
+        <v>601040</v>
       </c>
       <c r="R45" t="n">
-        <v>6276524</v>
+        <v>6276621</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5957,12 +5959,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5978,24 +5990,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Krister Aronsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Krister Aronsson, Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765510</t>
+          <t>https://artportalen.se/Sighting/78876600</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111198338</v>
+        <v>101765510</v>
       </c>
       <c r="B46" t="n">
         <v>41623</v>
@@ -6023,33 +6035,29 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601041</v>
+        <v>601080</v>
       </c>
       <c r="R46" t="n">
-        <v>6276563</v>
+        <v>6276524</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6073,22 +6081,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>22:58</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>22:58</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6097,33 +6095,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111198338</t>
+          <t>https://artportalen.se/Sighting/101765510</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15750722</v>
+        <v>111198338</v>
       </c>
       <c r="B47" t="n">
-        <v>41655</v>
+        <v>41623</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6131,21 +6130,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>215768</v>
+        <v>215755</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Längsbandad strimmätare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Horisme vitalbata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6153,11 +6152,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -6165,17 +6163,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>600995</v>
+        <v>601041</v>
       </c>
       <c r="R47" t="n">
-        <v>6276588</v>
+        <v>6276563</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6199,12 +6197,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2013-07-29</t>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2013-07-30</t>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6219,24 +6227,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15750722</t>
+          <t>https://artportalen.se/Sighting/111198338</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91021113</v>
+        <v>15750722</v>
       </c>
       <c r="B48" t="n">
         <v>41655</v>
@@ -6264,22 +6272,31 @@
           <t>(Hufnagel, 1767)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601042</v>
+        <v>600995</v>
       </c>
       <c r="R48" t="n">
-        <v>6276516</v>
+        <v>6276588</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6301,17 +6318,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2013-07-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6320,34 +6337,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mats Haglund</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91021113</t>
+          <t>https://artportalen.se/Sighting/15750722</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>70552066</v>
+        <v>91021113</v>
       </c>
       <c r="B49" t="n">
-        <v>41579</v>
+        <v>41655</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6355,51 +6371,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>215804</v>
+        <v>215768</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glimmalmätare</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Eupithecia venosata</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>600995</v>
+        <v>601042</v>
       </c>
       <c r="R49" t="n">
-        <v>6276588</v>
+        <v>6276516</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6421,27 +6425,17 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2014-07-02</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6450,33 +6444,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fred Ockruck</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fred Ockruck, Annette Bludau</t>
+          <t>Mats Haglund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70552066</t>
+          <t>https://artportalen.se/Sighting/91021113</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>101765489</v>
+        <v>70552066</v>
       </c>
       <c r="B50" t="n">
-        <v>42417</v>
+        <v>41579</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6484,46 +6479,54 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>215920</v>
+        <v>215804</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Glimmalmätare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Eupithecia venosata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>601080</v>
+        <v>600995</v>
       </c>
       <c r="R50" t="n">
-        <v>6276524</v>
+        <v>6276588</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6547,12 +6550,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2014-07-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2014-07-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6561,51 +6574,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Fred Ockruck</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Fred Ockruck, Annette Bludau</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765489</t>
+          <t>https://artportalen.se/Sighting/70552066</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101765499</v>
+        <v>101765489</v>
       </c>
       <c r="B51" t="n">
-        <v>42696</v>
+        <v>42417</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>216169</v>
+        <v>215920</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulbrunt nejlikfly</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hadena perplexa</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6691,56 +6703,60 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101765499</t>
+          <t>https://artportalen.se/Sighting/101765489</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2923897</v>
+        <v>101765499</v>
       </c>
       <c r="B52" t="n">
-        <v>99096</v>
+        <v>42696</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>216169</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gulbrunt nejlikfly</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hadena perplexa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601120</v>
+        <v>601080</v>
       </c>
       <c r="R52" t="n">
-        <v>6276584</v>
+        <v>6276524</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6767,12 +6783,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6781,39 +6797,31 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>f.d. banvall, kalkrik sand</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2923897</t>
+          <t>https://artportalen.se/Sighting/101765499</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>60558553</v>
+        <v>2923897</v>
       </c>
       <c r="B53" t="n">
         <v>99096</v>
@@ -6842,19 +6850,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601112</v>
+        <v>601120</v>
       </c>
       <c r="R53" t="n">
-        <v>6276479</v>
+        <v>6276584</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6876,22 +6886,17 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>de är verkligen annorlunda mot andra i mittlandet, lite klorofyll, tanigare luden, ljusa blommor etc.</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6902,16 +6907,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>f.d. banvall, kalkrik sand</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6921,13 +6931,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60558553</t>
+          <t>https://artportalen.se/Sighting/2923897</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>72341660</v>
+        <v>60558553</v>
       </c>
       <c r="B54" t="n">
         <v>99096</v>
@@ -6957,23 +6967,18 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dörby tallskog, nära sandheden, Öl</t>
+          <t>Gårdby sandhed NO, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601129</v>
+        <v>601112</v>
       </c>
       <c r="R54" t="n">
-        <v>6276608</v>
+        <v>6276479</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6995,17 +7000,22 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>de är verkligen annorlunda mot andra i mittlandet, lite klorofyll, tanigare luden, ljusa blommor etc.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7014,19 +7024,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -7036,13 +7045,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72341660</t>
+          <t>https://artportalen.se/Sighting/60558553</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102606674</v>
+        <v>72341660</v>
       </c>
       <c r="B55" t="n">
         <v>99096</v>
@@ -7074,24 +7083,24 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, nära sandheden, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601135</v>
+        <v>601129</v>
       </c>
       <c r="R55" t="n">
-        <v>6276471</v>
+        <v>6276608</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7110,17 +7119,17 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7133,84 +7142,80 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Barrskog (gles) på sand</t>
-        </is>
-      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Anders Svenson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>Botanikdagarna 2022 på Öland</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102606674</t>
+          <t>https://artportalen.se/Sighting/72341660</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>16768534</v>
+        <v>102606674</v>
       </c>
       <c r="B56" t="n">
-        <v>109814</v>
+        <v>99096</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220204</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gårdby sandhed norr, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>601064</v>
+        <v>601135</v>
       </c>
       <c r="R56" t="n">
-        <v>6276544</v>
+        <v>6276471</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7229,17 +7234,17 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2014-10-20</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7248,39 +7253,40 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>Barrskog (gles) på sand</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Jan Yngve Andersson, Anders Svenson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Botanikdagarna 2022 på Öland</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16768534</t>
+          <t>https://artportalen.se/Sighting/102606674</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>53995374</v>
+        <v>16768534</v>
       </c>
       <c r="B57" t="n">
         <v>109814</v>
@@ -7318,14 +7324,14 @@
       <c r="L57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gårdby sandhed N, Öl</t>
+          <t>Gårdby sandhed norr, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>601065</v>
+        <v>601064</v>
       </c>
       <c r="R57" t="n">
-        <v>6276542</v>
+        <v>6276544</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7352,12 +7358,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2015-06-19</t>
+          <t>2014-10-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7371,18 +7377,18 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Tallskogsbryn</t>
+          <t>skogsväg</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7392,16 +7398,16 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53995374</t>
+          <t>https://artportalen.se/Sighting/16768534</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124923374</v>
+        <v>53995374</v>
       </c>
       <c r="B58" t="n">
-        <v>109815</v>
+        <v>109814</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7427,21 +7433,23 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed N, Öl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>601029</v>
+        <v>601065</v>
       </c>
       <c r="R58" t="n">
-        <v>6276548</v>
+        <v>6276542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7463,27 +7471,17 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2015-06-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2015-06-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7494,28 +7492,37 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Tallskogsbryn</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124923374</t>
+          <t>https://artportalen.se/Sighting/53995374</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124946986</v>
+        <v>124923374</v>
       </c>
       <c r="B59" t="n">
         <v>109815</v>
@@ -7544,24 +7551,21 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gårdby sandhed norr, Öl</t>
+          <t>Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600964</v>
+        <v>601029</v>
       </c>
       <c r="R59" t="n">
-        <v>6276616</v>
+        <v>6276548</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7583,7 +7587,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7591,47 +7595,51 @@
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-10</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>öppen sand vid körväg</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Stefan Svenaeus, Heléne Wertwein Haavikko, Irene Järlebring, Lars Rigbäck, Bo Andersson, Natalie Henriksson Osbeck, Tommy Carlström, Mats Blomstedt, Ingela Carlström, Anders Waldenström, Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946986</t>
+          <t>https://artportalen.se/Sighting/124923374</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125873636</v>
+        <v>124946986</v>
       </c>
       <c r="B60" t="n">
         <v>109815</v>
@@ -7660,16 +7668,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed norr, Öl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>601097</v>
+        <v>600964</v>
       </c>
       <c r="R60" t="n">
-        <v>6276506</v>
+        <v>6276616</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7691,17 +7707,17 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7710,33 +7726,39 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>öppen sand vid körväg</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Ove Grönlund</t>
+          <t>Stefan Svenaeus, Heléne Wertwein Haavikko, Irene Järlebring, Lars Rigbäck, Bo Andersson, Natalie Henriksson Osbeck, Tommy Carlström, Mats Blomstedt, Ingela Carlström, Anders Waldenström, Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125873636</t>
+          <t>https://artportalen.se/Sighting/124946986</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72341663</v>
+        <v>125873636</v>
       </c>
       <c r="B61" t="n">
-        <v>107516</v>
+        <v>109815</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7744,16 +7766,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7762,20 +7784,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Dörby tallskog, nära sandheden, Öl</t>
+          <t>Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>601129</v>
+        <v>601097</v>
       </c>
       <c r="R61" t="n">
-        <v>6276608</v>
+        <v>6276506</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7797,17 +7815,17 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7816,35 +7834,30 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Ove Grönlund</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72341663</t>
+          <t>https://artportalen.se/Sighting/125873636</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>90968272</v>
+        <v>72341663</v>
       </c>
       <c r="B62" t="n">
         <v>107516</v>
@@ -7873,16 +7886,20 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gårdby sandstäpp, Öl</t>
+          <t>Dörby tallskog, nära sandheden, Öl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>601036</v>
+        <v>601129</v>
       </c>
       <c r="R62" t="n">
-        <v>6276547</v>
+        <v>6276608</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7904,17 +7921,17 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7923,42 +7940,38 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Betad kalkgräsmark</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eric Lundén</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cassandra Hallman</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90968272</t>
+          <t>https://artportalen.se/Sighting/72341663</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>87452574</v>
+        <v>90968272</v>
       </c>
       <c r="B63" t="n">
-        <v>107060</v>
+        <v>107516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7966,16 +7979,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7984,24 +7997,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gårdby sandhed N, Öl</t>
+          <t>Gårdby sandstäpp, Öl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>601010</v>
+        <v>601036</v>
       </c>
       <c r="R63" t="n">
-        <v>6276582</v>
+        <v>6276547</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8023,17 +8028,17 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8042,38 +8047,42 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Betad kalkgräsmark</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Per Ahlgren</t>
+          <t>Eric Lundén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Stefan Björn, Per Ahlgren</t>
+          <t>Cassandra Hallman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87452574</t>
+          <t>https://artportalen.se/Sighting/90968272</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>60558453</v>
+        <v>87452574</v>
       </c>
       <c r="B64" t="n">
-        <v>98050</v>
+        <v>107060</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8081,45 +8090,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222112</v>
+        <v>221903</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO, Öl</t>
+          <t>Gårdby sandhed N, Öl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>601112</v>
+        <v>601010</v>
       </c>
       <c r="R64" t="n">
-        <v>6276479</v>
+        <v>6276582</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8141,17 +8147,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8160,18 +8166,19 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Per Ahlgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Stefan Björn, Per Ahlgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8181,16 +8188,16 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60558453</t>
+          <t>https://artportalen.se/Sighting/87452574</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5141664</v>
+        <v>60558453</v>
       </c>
       <c r="B65" t="n">
-        <v>100797</v>
+        <v>98050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8198,34 +8205,45 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222617</v>
+        <v>222112</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Gårdby sandhed NO, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>601093</v>
+        <v>601112</v>
       </c>
       <c r="R65" t="n">
-        <v>6276554</v>
+        <v>6276479</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8247,22 +8265,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8273,21 +8286,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8297,13 +8305,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5141664</t>
+          <t>https://artportalen.se/Sighting/60558453</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>54136165</v>
+        <v>5141664</v>
       </c>
       <c r="B66" t="n">
         <v>100797</v>
@@ -8332,26 +8340,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NO., Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>601088</v>
+        <v>601093</v>
       </c>
       <c r="R66" t="n">
-        <v>6276505</v>
+        <v>6276554</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8370,17 +8371,22 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Gårdby</t>
+          <t>Norra Möckleby</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8391,16 +8397,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>tallskog med lövinslag</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8410,16 +8421,16 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54136165</t>
+          <t>https://artportalen.se/Sighting/5141664</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124946779</v>
+        <v>54136165</v>
       </c>
       <c r="B67" t="n">
-        <v>100798</v>
+        <v>100797</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8446,22 +8457,25 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gårdby sandhed NR, Öl</t>
+          <t>Gårdby sandhed NO., Öl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>601035</v>
+        <v>601088</v>
       </c>
       <c r="R67" t="n">
-        <v>6276550</v>
+        <v>6276505</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8485,12 +8499,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8499,61 +8513,59 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>betad sandgräshed</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124946779</t>
+          <t>https://artportalen.se/Sighting/54136165</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125545586</v>
+        <v>124946779</v>
       </c>
       <c r="B68" t="n">
-        <v>101345</v>
+        <v>100798</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222886</v>
+        <v>222617</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8563,17 +8575,17 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Galgrör, Galgrör, Öl</t>
+          <t>Gårdby sandhed NR, Öl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>601082</v>
+        <v>601035</v>
       </c>
       <c r="R68" t="n">
-        <v>6276507</v>
+        <v>6276550</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8597,22 +8609,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8621,72 +8623,81 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>betad sandgräshed</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist, Andreas Källman</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Waldenström, Ingela Carlström, Mats Blomstedt, Tommy Carlström, Natalie Henriksson Osbeck, Bo Andersson, Lars Rigbäck, Irene Järlebring, Heléne Wertwein Haavikko, Stefan Svenaeus</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125545586</t>
+          <t>https://artportalen.se/Sighting/124946779</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6181704</v>
+        <v>125545586</v>
       </c>
       <c r="B69" t="n">
-        <v>107062</v>
+        <v>101345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>224354</v>
+        <v>222886</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Galgrör, Galgrör, Öl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>601114</v>
+        <v>601082</v>
       </c>
       <c r="R69" t="n">
-        <v>6276570</v>
+        <v>6276507</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8705,22 +8716,27 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Norra Möckleby</t>
+          <t>Gårdby</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8731,84 +8747,67 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Andreas Lundqvist, Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6181704</t>
+          <t>https://artportalen.se/Sighting/125545586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>62497754</v>
+        <v>6181704</v>
       </c>
       <c r="B70" t="n">
-        <v>13027</v>
+        <v>107062</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>236198</v>
+        <v>224354</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vanlig axveronika</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Villa longicornis</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Lyneborg, 1965</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>Veronica spicata subsp. spicata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, väg N om, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600989</v>
+        <v>601114</v>
       </c>
       <c r="R70" t="n">
-        <v>6276600</v>
+        <v>6276570</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8835,12 +8834,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8854,32 +8858,152 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>sandig brukningsväg</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>Jan Edelsjö</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>NHRS-JEDS000006494</t>
+          <t>tallskog med lövinslag</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6181704</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>62497754</v>
+      </c>
+      <c r="B71" t="n">
+        <v>13027</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>236198</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Villa longicornis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Lyneborg, 1965</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gårdby sandhed, väg N om, Öl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>600989</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6276600</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>sandig brukningsväg</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
           <t>Jan Edelsjö</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>NHRS-JEDS000006494</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Edelsjö</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Jan Edelsjö, Niklas Lönnell, Johan Nilsson, Jonas Sandström</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62497754</t>
         </is>
@@ -8956,6 +9080,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2023 artfynd.xlsx
+++ b/artfynd/A 42099-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>136475997</v>
       </c>
       <c r="B12" t="n">
-        <v>87096</v>
+        <v>87097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
